--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4083,7 +4083,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>156</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4388,7 +4388,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>164</v>
       </c>
@@ -4403,13 +4403,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4491,7 +4491,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>168</v>
       </c>
@@ -4506,13 +4506,13 @@
         <v>169</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4800,7 +4800,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>182</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
